--- a/templates/excel/初期設定_記入シート.xlsx
+++ b/templates/excel/初期設定_記入シート.xlsx
@@ -1,14 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="商品メニュー" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="名簿" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="商品メニュー" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="名簿" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="キャスト別バック" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -890,12 +891,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C75"/>
+  <dimension ref="A1:E75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -949,12 +952,22 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
+          <t>読み仮名</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
           <t>ランク(あれば)</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>区分</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>入店日(あれば)</t>
         </is>
       </c>
     </row>
@@ -966,12 +979,22 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
+          <t>ここ</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
           <t>レギュラー</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>在籍</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -983,12 +1006,22 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
+          <t>りん</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
           <t>なし</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>体験入店</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -996,151 +1029,211 @@
       <c r="A11" s="7" t="n"/>
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
+      <c r="D11" s="7" t="n"/>
+      <c r="E11" s="7" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n"/>
       <c r="B12" s="7" t="n"/>
       <c r="C12" s="7" t="n"/>
+      <c r="D12" s="7" t="n"/>
+      <c r="E12" s="7" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n"/>
       <c r="B13" s="7" t="n"/>
       <c r="C13" s="7" t="n"/>
+      <c r="D13" s="7" t="n"/>
+      <c r="E13" s="7" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n"/>
       <c r="B14" s="7" t="n"/>
       <c r="C14" s="7" t="n"/>
+      <c r="D14" s="7" t="n"/>
+      <c r="E14" s="7" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n"/>
       <c r="B15" s="7" t="n"/>
       <c r="C15" s="7" t="n"/>
+      <c r="D15" s="7" t="n"/>
+      <c r="E15" s="7" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n"/>
       <c r="B16" s="7" t="n"/>
       <c r="C16" s="7" t="n"/>
+      <c r="D16" s="7" t="n"/>
+      <c r="E16" s="7" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n"/>
       <c r="B17" s="7" t="n"/>
       <c r="C17" s="7" t="n"/>
+      <c r="D17" s="7" t="n"/>
+      <c r="E17" s="7" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n"/>
       <c r="B18" s="7" t="n"/>
       <c r="C18" s="7" t="n"/>
+      <c r="D18" s="7" t="n"/>
+      <c r="E18" s="7" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n"/>
       <c r="B19" s="7" t="n"/>
       <c r="C19" s="7" t="n"/>
+      <c r="D19" s="7" t="n"/>
+      <c r="E19" s="7" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n"/>
       <c r="B20" s="7" t="n"/>
       <c r="C20" s="7" t="n"/>
+      <c r="D20" s="7" t="n"/>
+      <c r="E20" s="7" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n"/>
       <c r="B21" s="7" t="n"/>
       <c r="C21" s="7" t="n"/>
+      <c r="D21" s="7" t="n"/>
+      <c r="E21" s="7" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n"/>
       <c r="B22" s="7" t="n"/>
       <c r="C22" s="7" t="n"/>
+      <c r="D22" s="7" t="n"/>
+      <c r="E22" s="7" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n"/>
       <c r="B23" s="7" t="n"/>
       <c r="C23" s="7" t="n"/>
+      <c r="D23" s="7" t="n"/>
+      <c r="E23" s="7" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n"/>
       <c r="B24" s="7" t="n"/>
       <c r="C24" s="7" t="n"/>
+      <c r="D24" s="7" t="n"/>
+      <c r="E24" s="7" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n"/>
       <c r="B25" s="7" t="n"/>
       <c r="C25" s="7" t="n"/>
+      <c r="D25" s="7" t="n"/>
+      <c r="E25" s="7" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n"/>
       <c r="B26" s="7" t="n"/>
       <c r="C26" s="7" t="n"/>
+      <c r="D26" s="7" t="n"/>
+      <c r="E26" s="7" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n"/>
       <c r="B27" s="7" t="n"/>
       <c r="C27" s="7" t="n"/>
+      <c r="D27" s="7" t="n"/>
+      <c r="E27" s="7" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n"/>
       <c r="B28" s="7" t="n"/>
       <c r="C28" s="7" t="n"/>
+      <c r="D28" s="7" t="n"/>
+      <c r="E28" s="7" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n"/>
       <c r="B29" s="7" t="n"/>
       <c r="C29" s="7" t="n"/>
+      <c r="D29" s="7" t="n"/>
+      <c r="E29" s="7" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n"/>
       <c r="B30" s="7" t="n"/>
       <c r="C30" s="7" t="n"/>
+      <c r="D30" s="7" t="n"/>
+      <c r="E30" s="7" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n"/>
       <c r="B31" s="7" t="n"/>
       <c r="C31" s="7" t="n"/>
+      <c r="D31" s="7" t="n"/>
+      <c r="E31" s="7" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n"/>
       <c r="B32" s="7" t="n"/>
       <c r="C32" s="7" t="n"/>
+      <c r="D32" s="7" t="n"/>
+      <c r="E32" s="7" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n"/>
       <c r="B33" s="7" t="n"/>
       <c r="C33" s="7" t="n"/>
+      <c r="D33" s="7" t="n"/>
+      <c r="E33" s="7" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n"/>
       <c r="B34" s="7" t="n"/>
       <c r="C34" s="7" t="n"/>
+      <c r="D34" s="7" t="n"/>
+      <c r="E34" s="7" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n"/>
       <c r="B35" s="7" t="n"/>
       <c r="C35" s="7" t="n"/>
+      <c r="D35" s="7" t="n"/>
+      <c r="E35" s="7" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n"/>
       <c r="B36" s="7" t="n"/>
       <c r="C36" s="7" t="n"/>
+      <c r="D36" s="7" t="n"/>
+      <c r="E36" s="7" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n"/>
       <c r="B37" s="7" t="n"/>
       <c r="C37" s="7" t="n"/>
+      <c r="D37" s="7" t="n"/>
+      <c r="E37" s="7" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n"/>
       <c r="B38" s="7" t="n"/>
       <c r="C38" s="7" t="n"/>
+      <c r="D38" s="7" t="n"/>
+      <c r="E38" s="7" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n"/>
       <c r="B39" s="7" t="n"/>
       <c r="C39" s="7" t="n"/>
+      <c r="D39" s="7" t="n"/>
+      <c r="E39" s="7" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n"/>
       <c r="B40" s="7" t="n"/>
       <c r="C40" s="7" t="n"/>
+      <c r="D40" s="7" t="n"/>
+      <c r="E40" s="7" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -1157,7 +1250,17 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
+          <t>読み仮名</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
           <t>職種</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>入店日(あれば)</t>
         </is>
       </c>
     </row>
@@ -1169,7 +1272,17 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
+          <t>やまだ</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
           <t>ボーイ</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -1181,139 +1294,491 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
+          <t>たなか</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
           <t>キッチン</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n"/>
       <c r="B46" s="7" t="n"/>
+      <c r="C46" s="7" t="n"/>
+      <c r="D46" s="7" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n"/>
       <c r="B47" s="7" t="n"/>
+      <c r="C47" s="7" t="n"/>
+      <c r="D47" s="7" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n"/>
       <c r="B48" s="7" t="n"/>
+      <c r="C48" s="7" t="n"/>
+      <c r="D48" s="7" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n"/>
       <c r="B49" s="7" t="n"/>
+      <c r="C49" s="7" t="n"/>
+      <c r="D49" s="7" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n"/>
       <c r="B50" s="7" t="n"/>
+      <c r="C50" s="7" t="n"/>
+      <c r="D50" s="7" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n"/>
       <c r="B51" s="7" t="n"/>
+      <c r="C51" s="7" t="n"/>
+      <c r="D51" s="7" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n"/>
       <c r="B52" s="7" t="n"/>
+      <c r="C52" s="7" t="n"/>
+      <c r="D52" s="7" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n"/>
       <c r="B53" s="7" t="n"/>
+      <c r="C53" s="7" t="n"/>
+      <c r="D53" s="7" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n"/>
       <c r="B54" s="7" t="n"/>
+      <c r="C54" s="7" t="n"/>
+      <c r="D54" s="7" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n"/>
       <c r="B55" s="7" t="n"/>
+      <c r="C55" s="7" t="n"/>
+      <c r="D55" s="7" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n"/>
       <c r="B56" s="7" t="n"/>
+      <c r="C56" s="7" t="n"/>
+      <c r="D56" s="7" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n"/>
       <c r="B57" s="7" t="n"/>
+      <c r="C57" s="7" t="n"/>
+      <c r="D57" s="7" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n"/>
       <c r="B58" s="7" t="n"/>
+      <c r="C58" s="7" t="n"/>
+      <c r="D58" s="7" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="7" t="n"/>
       <c r="B59" s="7" t="n"/>
+      <c r="C59" s="7" t="n"/>
+      <c r="D59" s="7" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n"/>
       <c r="B60" s="7" t="n"/>
+      <c r="C60" s="7" t="n"/>
+      <c r="D60" s="7" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="7" t="n"/>
       <c r="B61" s="7" t="n"/>
+      <c r="C61" s="7" t="n"/>
+      <c r="D61" s="7" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n"/>
       <c r="B62" s="7" t="n"/>
+      <c r="C62" s="7" t="n"/>
+      <c r="D62" s="7" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n"/>
       <c r="B63" s="7" t="n"/>
+      <c r="C63" s="7" t="n"/>
+      <c r="D63" s="7" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n"/>
       <c r="B64" s="7" t="n"/>
+      <c r="C64" s="7" t="n"/>
+      <c r="D64" s="7" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n"/>
       <c r="B65" s="7" t="n"/>
+      <c r="C65" s="7" t="n"/>
+      <c r="D65" s="7" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n"/>
       <c r="B66" s="7" t="n"/>
+      <c r="C66" s="7" t="n"/>
+      <c r="D66" s="7" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n"/>
       <c r="B67" s="7" t="n"/>
+      <c r="C67" s="7" t="n"/>
+      <c r="D67" s="7" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n"/>
       <c r="B68" s="7" t="n"/>
+      <c r="C68" s="7" t="n"/>
+      <c r="D68" s="7" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n"/>
       <c r="B69" s="7" t="n"/>
+      <c r="C69" s="7" t="n"/>
+      <c r="D69" s="7" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n"/>
       <c r="B70" s="7" t="n"/>
+      <c r="C70" s="7" t="n"/>
+      <c r="D70" s="7" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="7" t="n"/>
       <c r="B71" s="7" t="n"/>
+      <c r="C71" s="7" t="n"/>
+      <c r="D71" s="7" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="7" t="n"/>
       <c r="B72" s="7" t="n"/>
+      <c r="C72" s="7" t="n"/>
+      <c r="D72" s="7" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="7" t="n"/>
       <c r="B73" s="7" t="n"/>
+      <c r="C73" s="7" t="n"/>
+      <c r="D73" s="7" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n"/>
       <c r="B74" s="7" t="n"/>
+      <c r="C74" s="7" t="n"/>
+      <c r="D74" s="7" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="7" t="n"/>
       <c r="B75" s="7" t="n"/>
+      <c r="C75" s="7" t="n"/>
+      <c r="D75" s="7" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="C11:C40" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="入力エラー" error="リストから選んでください" type="list">
-      <formula1>"在籍,体験入店"</formula1>
+    <dataValidation sqref="D11:D40" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="入力エラー" error="リストから選んでください" type="list">
+      <formula1>"在籍,体験入店,派遣,日払い"</formula1>
     </dataValidation>
-    <dataValidation sqref="B46:B75" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="入力エラー" error="リストから選んでください" type="list">
+    <dataValidation sqref="C46:C75" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="入力エラー" error="リストから選んでください" type="list">
       <formula1>"ボーイ,キッチン,店長,その他"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C42"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>キャスト別バック</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>店舗名</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>※灰色の行は記入例です。消して上書きするか、下の空欄に書いてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>※基本は、訪問時にお店の方がPOSへ入力します</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>※先に送る場合だけ、書いてください</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>※時給や本名などの個人情報は書かないでください</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>※書き終わったら、このファイル(またはシートのリンク)をLINEで送ってください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>キャストごとのバック</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>源氏名</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>バックの種類</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>額または率</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>ココ</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>指名</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>1000円</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>ココ</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>ドリンク</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="n"/>
+      <c r="B13" s="7" t="n"/>
+      <c r="C13" s="7" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="n"/>
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="7" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="n"/>
+      <c r="B15" s="7" t="n"/>
+      <c r="C15" s="7" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="n"/>
+      <c r="B16" s="7" t="n"/>
+      <c r="C16" s="7" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="n"/>
+      <c r="B17" s="7" t="n"/>
+      <c r="C17" s="7" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="n"/>
+      <c r="B18" s="7" t="n"/>
+      <c r="C18" s="7" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="n"/>
+      <c r="B19" s="7" t="n"/>
+      <c r="C19" s="7" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="n"/>
+      <c r="B20" s="7" t="n"/>
+      <c r="C20" s="7" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="n"/>
+      <c r="B21" s="7" t="n"/>
+      <c r="C21" s="7" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="n"/>
+      <c r="B22" s="7" t="n"/>
+      <c r="C22" s="7" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="n"/>
+      <c r="B23" s="7" t="n"/>
+      <c r="C23" s="7" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="n"/>
+      <c r="B24" s="7" t="n"/>
+      <c r="C24" s="7" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="n"/>
+      <c r="B25" s="7" t="n"/>
+      <c r="C25" s="7" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="n"/>
+      <c r="B26" s="7" t="n"/>
+      <c r="C26" s="7" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="n"/>
+      <c r="B27" s="7" t="n"/>
+      <c r="C27" s="7" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="n"/>
+      <c r="B28" s="7" t="n"/>
+      <c r="C28" s="7" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="n"/>
+      <c r="B29" s="7" t="n"/>
+      <c r="C29" s="7" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="n"/>
+      <c r="B30" s="7" t="n"/>
+      <c r="C30" s="7" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="n"/>
+      <c r="B31" s="7" t="n"/>
+      <c r="C31" s="7" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="n"/>
+      <c r="B32" s="7" t="n"/>
+      <c r="C32" s="7" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="n"/>
+      <c r="B33" s="7" t="n"/>
+      <c r="C33" s="7" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="n"/>
+      <c r="B34" s="7" t="n"/>
+      <c r="C34" s="7" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="n"/>
+      <c r="B35" s="7" t="n"/>
+      <c r="C35" s="7" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="n"/>
+      <c r="B36" s="7" t="n"/>
+      <c r="C36" s="7" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="n"/>
+      <c r="B37" s="7" t="n"/>
+      <c r="C37" s="7" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="n"/>
+      <c r="B38" s="7" t="n"/>
+      <c r="C38" s="7" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="n"/>
+      <c r="B39" s="7" t="n"/>
+      <c r="C39" s="7" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="n"/>
+      <c r="B40" s="7" t="n"/>
+      <c r="C40" s="7" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="n"/>
+      <c r="B41" s="7" t="n"/>
+      <c r="C41" s="7" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="n"/>
+      <c r="B42" s="7" t="n"/>
+      <c r="C42" s="7" t="n"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="B13:B42" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="入力エラー" error="リストから選んでください" type="list">
+      <formula1>"セット,延長,指名,担当卓の売上,ドリンク,ボトル,フード"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/templates/excel/初期設定_記入シート.xlsx
+++ b/templates/excel/初期設定_記入シート.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="商品メニュー" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="名簿" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="商品メニュー" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="名簿" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/templates/excel/初期設定_記入シート.xlsx
+++ b/templates/excel/初期設定_記入シート.xlsx
@@ -1507,12 +1507,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1585,7 +1586,12 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>額または率</t>
+          <t>単位</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>金額または率</t>
         </is>
       </c>
     </row>
@@ -1602,8 +1608,11 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>1000円</t>
-        </is>
+          <t>円</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>1000</v>
       </c>
     </row>
     <row r="12">
@@ -1619,164 +1628,203 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>20%</t>
-        </is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n"/>
       <c r="B13" s="7" t="n"/>
       <c r="C13" s="7" t="n"/>
+      <c r="D13" s="7" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n"/>
       <c r="B14" s="7" t="n"/>
       <c r="C14" s="7" t="n"/>
+      <c r="D14" s="7" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n"/>
       <c r="B15" s="7" t="n"/>
       <c r="C15" s="7" t="n"/>
+      <c r="D15" s="7" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n"/>
       <c r="B16" s="7" t="n"/>
       <c r="C16" s="7" t="n"/>
+      <c r="D16" s="7" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n"/>
       <c r="B17" s="7" t="n"/>
       <c r="C17" s="7" t="n"/>
+      <c r="D17" s="7" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n"/>
       <c r="B18" s="7" t="n"/>
       <c r="C18" s="7" t="n"/>
+      <c r="D18" s="7" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n"/>
       <c r="B19" s="7" t="n"/>
       <c r="C19" s="7" t="n"/>
+      <c r="D19" s="7" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n"/>
       <c r="B20" s="7" t="n"/>
       <c r="C20" s="7" t="n"/>
+      <c r="D20" s="7" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n"/>
       <c r="B21" s="7" t="n"/>
       <c r="C21" s="7" t="n"/>
+      <c r="D21" s="7" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n"/>
       <c r="B22" s="7" t="n"/>
       <c r="C22" s="7" t="n"/>
+      <c r="D22" s="7" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n"/>
       <c r="B23" s="7" t="n"/>
       <c r="C23" s="7" t="n"/>
+      <c r="D23" s="7" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n"/>
       <c r="B24" s="7" t="n"/>
       <c r="C24" s="7" t="n"/>
+      <c r="D24" s="7" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n"/>
       <c r="B25" s="7" t="n"/>
       <c r="C25" s="7" t="n"/>
+      <c r="D25" s="7" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n"/>
       <c r="B26" s="7" t="n"/>
       <c r="C26" s="7" t="n"/>
+      <c r="D26" s="7" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n"/>
       <c r="B27" s="7" t="n"/>
       <c r="C27" s="7" t="n"/>
+      <c r="D27" s="7" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n"/>
       <c r="B28" s="7" t="n"/>
       <c r="C28" s="7" t="n"/>
+      <c r="D28" s="7" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n"/>
       <c r="B29" s="7" t="n"/>
       <c r="C29" s="7" t="n"/>
+      <c r="D29" s="7" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n"/>
       <c r="B30" s="7" t="n"/>
       <c r="C30" s="7" t="n"/>
+      <c r="D30" s="7" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n"/>
       <c r="B31" s="7" t="n"/>
       <c r="C31" s="7" t="n"/>
+      <c r="D31" s="7" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n"/>
       <c r="B32" s="7" t="n"/>
       <c r="C32" s="7" t="n"/>
+      <c r="D32" s="7" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n"/>
       <c r="B33" s="7" t="n"/>
       <c r="C33" s="7" t="n"/>
+      <c r="D33" s="7" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n"/>
       <c r="B34" s="7" t="n"/>
       <c r="C34" s="7" t="n"/>
+      <c r="D34" s="7" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n"/>
       <c r="B35" s="7" t="n"/>
       <c r="C35" s="7" t="n"/>
+      <c r="D35" s="7" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n"/>
       <c r="B36" s="7" t="n"/>
       <c r="C36" s="7" t="n"/>
+      <c r="D36" s="7" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n"/>
       <c r="B37" s="7" t="n"/>
       <c r="C37" s="7" t="n"/>
+      <c r="D37" s="7" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n"/>
       <c r="B38" s="7" t="n"/>
       <c r="C38" s="7" t="n"/>
+      <c r="D38" s="7" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n"/>
       <c r="B39" s="7" t="n"/>
       <c r="C39" s="7" t="n"/>
+      <c r="D39" s="7" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n"/>
       <c r="B40" s="7" t="n"/>
       <c r="C40" s="7" t="n"/>
+      <c r="D40" s="7" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n"/>
       <c r="B41" s="7" t="n"/>
       <c r="C41" s="7" t="n"/>
+      <c r="D41" s="7" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n"/>
       <c r="B42" s="7" t="n"/>
       <c r="C42" s="7" t="n"/>
+      <c r="D42" s="7" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
+  <dataValidations count="3">
     <dataValidation sqref="B13:B42" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="入力エラー" error="リストから選んでください" type="list">
       <formula1>"セット,延長,指名,担当卓の売上,ドリンク,ボトル,フード"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C13:C42" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="入力エラー" error="リストから選んでください" type="list">
+      <formula1>"円,%"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D13:D42" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="入力エラー" error="0以上の数字で入力してください" type="decimal" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/templates/excel/初期設定_記入シート.xlsx
+++ b/templates/excel/初期設定_記入シート.xlsx
@@ -1,14 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="商品メニュー" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="名簿" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="商品メニュー" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="名簿" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="キャスト別バック" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -890,12 +891,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C75"/>
+  <dimension ref="A1:E75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -949,12 +952,22 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
+          <t>読み仮名</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
           <t>ランク(あれば)</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>区分</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>入店日(あれば)</t>
         </is>
       </c>
     </row>
@@ -966,12 +979,22 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
+          <t>ここ</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
           <t>レギュラー</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>在籍</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -983,12 +1006,22 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
+          <t>りん</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
           <t>なし</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>体験入店</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -996,151 +1029,211 @@
       <c r="A11" s="7" t="n"/>
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
+      <c r="D11" s="7" t="n"/>
+      <c r="E11" s="7" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n"/>
       <c r="B12" s="7" t="n"/>
       <c r="C12" s="7" t="n"/>
+      <c r="D12" s="7" t="n"/>
+      <c r="E12" s="7" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n"/>
       <c r="B13" s="7" t="n"/>
       <c r="C13" s="7" t="n"/>
+      <c r="D13" s="7" t="n"/>
+      <c r="E13" s="7" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n"/>
       <c r="B14" s="7" t="n"/>
       <c r="C14" s="7" t="n"/>
+      <c r="D14" s="7" t="n"/>
+      <c r="E14" s="7" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n"/>
       <c r="B15" s="7" t="n"/>
       <c r="C15" s="7" t="n"/>
+      <c r="D15" s="7" t="n"/>
+      <c r="E15" s="7" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n"/>
       <c r="B16" s="7" t="n"/>
       <c r="C16" s="7" t="n"/>
+      <c r="D16" s="7" t="n"/>
+      <c r="E16" s="7" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n"/>
       <c r="B17" s="7" t="n"/>
       <c r="C17" s="7" t="n"/>
+      <c r="D17" s="7" t="n"/>
+      <c r="E17" s="7" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n"/>
       <c r="B18" s="7" t="n"/>
       <c r="C18" s="7" t="n"/>
+      <c r="D18" s="7" t="n"/>
+      <c r="E18" s="7" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n"/>
       <c r="B19" s="7" t="n"/>
       <c r="C19" s="7" t="n"/>
+      <c r="D19" s="7" t="n"/>
+      <c r="E19" s="7" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n"/>
       <c r="B20" s="7" t="n"/>
       <c r="C20" s="7" t="n"/>
+      <c r="D20" s="7" t="n"/>
+      <c r="E20" s="7" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n"/>
       <c r="B21" s="7" t="n"/>
       <c r="C21" s="7" t="n"/>
+      <c r="D21" s="7" t="n"/>
+      <c r="E21" s="7" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n"/>
       <c r="B22" s="7" t="n"/>
       <c r="C22" s="7" t="n"/>
+      <c r="D22" s="7" t="n"/>
+      <c r="E22" s="7" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n"/>
       <c r="B23" s="7" t="n"/>
       <c r="C23" s="7" t="n"/>
+      <c r="D23" s="7" t="n"/>
+      <c r="E23" s="7" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n"/>
       <c r="B24" s="7" t="n"/>
       <c r="C24" s="7" t="n"/>
+      <c r="D24" s="7" t="n"/>
+      <c r="E24" s="7" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n"/>
       <c r="B25" s="7" t="n"/>
       <c r="C25" s="7" t="n"/>
+      <c r="D25" s="7" t="n"/>
+      <c r="E25" s="7" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n"/>
       <c r="B26" s="7" t="n"/>
       <c r="C26" s="7" t="n"/>
+      <c r="D26" s="7" t="n"/>
+      <c r="E26" s="7" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n"/>
       <c r="B27" s="7" t="n"/>
       <c r="C27" s="7" t="n"/>
+      <c r="D27" s="7" t="n"/>
+      <c r="E27" s="7" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n"/>
       <c r="B28" s="7" t="n"/>
       <c r="C28" s="7" t="n"/>
+      <c r="D28" s="7" t="n"/>
+      <c r="E28" s="7" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n"/>
       <c r="B29" s="7" t="n"/>
       <c r="C29" s="7" t="n"/>
+      <c r="D29" s="7" t="n"/>
+      <c r="E29" s="7" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n"/>
       <c r="B30" s="7" t="n"/>
       <c r="C30" s="7" t="n"/>
+      <c r="D30" s="7" t="n"/>
+      <c r="E30" s="7" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n"/>
       <c r="B31" s="7" t="n"/>
       <c r="C31" s="7" t="n"/>
+      <c r="D31" s="7" t="n"/>
+      <c r="E31" s="7" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n"/>
       <c r="B32" s="7" t="n"/>
       <c r="C32" s="7" t="n"/>
+      <c r="D32" s="7" t="n"/>
+      <c r="E32" s="7" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n"/>
       <c r="B33" s="7" t="n"/>
       <c r="C33" s="7" t="n"/>
+      <c r="D33" s="7" t="n"/>
+      <c r="E33" s="7" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n"/>
       <c r="B34" s="7" t="n"/>
       <c r="C34" s="7" t="n"/>
+      <c r="D34" s="7" t="n"/>
+      <c r="E34" s="7" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n"/>
       <c r="B35" s="7" t="n"/>
       <c r="C35" s="7" t="n"/>
+      <c r="D35" s="7" t="n"/>
+      <c r="E35" s="7" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n"/>
       <c r="B36" s="7" t="n"/>
       <c r="C36" s="7" t="n"/>
+      <c r="D36" s="7" t="n"/>
+      <c r="E36" s="7" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n"/>
       <c r="B37" s="7" t="n"/>
       <c r="C37" s="7" t="n"/>
+      <c r="D37" s="7" t="n"/>
+      <c r="E37" s="7" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n"/>
       <c r="B38" s="7" t="n"/>
       <c r="C38" s="7" t="n"/>
+      <c r="D38" s="7" t="n"/>
+      <c r="E38" s="7" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n"/>
       <c r="B39" s="7" t="n"/>
       <c r="C39" s="7" t="n"/>
+      <c r="D39" s="7" t="n"/>
+      <c r="E39" s="7" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n"/>
       <c r="B40" s="7" t="n"/>
       <c r="C40" s="7" t="n"/>
+      <c r="D40" s="7" t="n"/>
+      <c r="E40" s="7" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -1157,7 +1250,17 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
+          <t>読み仮名</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
           <t>職種</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>入店日(あれば)</t>
         </is>
       </c>
     </row>
@@ -1169,7 +1272,17 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
+          <t>やまだ</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
           <t>ボーイ</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -1181,139 +1294,539 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
+          <t>たなか</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
           <t>キッチン</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n"/>
       <c r="B46" s="7" t="n"/>
+      <c r="C46" s="7" t="n"/>
+      <c r="D46" s="7" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n"/>
       <c r="B47" s="7" t="n"/>
+      <c r="C47" s="7" t="n"/>
+      <c r="D47" s="7" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n"/>
       <c r="B48" s="7" t="n"/>
+      <c r="C48" s="7" t="n"/>
+      <c r="D48" s="7" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n"/>
       <c r="B49" s="7" t="n"/>
+      <c r="C49" s="7" t="n"/>
+      <c r="D49" s="7" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n"/>
       <c r="B50" s="7" t="n"/>
+      <c r="C50" s="7" t="n"/>
+      <c r="D50" s="7" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n"/>
       <c r="B51" s="7" t="n"/>
+      <c r="C51" s="7" t="n"/>
+      <c r="D51" s="7" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n"/>
       <c r="B52" s="7" t="n"/>
+      <c r="C52" s="7" t="n"/>
+      <c r="D52" s="7" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n"/>
       <c r="B53" s="7" t="n"/>
+      <c r="C53" s="7" t="n"/>
+      <c r="D53" s="7" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n"/>
       <c r="B54" s="7" t="n"/>
+      <c r="C54" s="7" t="n"/>
+      <c r="D54" s="7" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n"/>
       <c r="B55" s="7" t="n"/>
+      <c r="C55" s="7" t="n"/>
+      <c r="D55" s="7" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n"/>
       <c r="B56" s="7" t="n"/>
+      <c r="C56" s="7" t="n"/>
+      <c r="D56" s="7" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n"/>
       <c r="B57" s="7" t="n"/>
+      <c r="C57" s="7" t="n"/>
+      <c r="D57" s="7" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n"/>
       <c r="B58" s="7" t="n"/>
+      <c r="C58" s="7" t="n"/>
+      <c r="D58" s="7" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="7" t="n"/>
       <c r="B59" s="7" t="n"/>
+      <c r="C59" s="7" t="n"/>
+      <c r="D59" s="7" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n"/>
       <c r="B60" s="7" t="n"/>
+      <c r="C60" s="7" t="n"/>
+      <c r="D60" s="7" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="7" t="n"/>
       <c r="B61" s="7" t="n"/>
+      <c r="C61" s="7" t="n"/>
+      <c r="D61" s="7" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n"/>
       <c r="B62" s="7" t="n"/>
+      <c r="C62" s="7" t="n"/>
+      <c r="D62" s="7" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n"/>
       <c r="B63" s="7" t="n"/>
+      <c r="C63" s="7" t="n"/>
+      <c r="D63" s="7" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n"/>
       <c r="B64" s="7" t="n"/>
+      <c r="C64" s="7" t="n"/>
+      <c r="D64" s="7" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n"/>
       <c r="B65" s="7" t="n"/>
+      <c r="C65" s="7" t="n"/>
+      <c r="D65" s="7" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n"/>
       <c r="B66" s="7" t="n"/>
+      <c r="C66" s="7" t="n"/>
+      <c r="D66" s="7" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n"/>
       <c r="B67" s="7" t="n"/>
+      <c r="C67" s="7" t="n"/>
+      <c r="D67" s="7" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n"/>
       <c r="B68" s="7" t="n"/>
+      <c r="C68" s="7" t="n"/>
+      <c r="D68" s="7" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n"/>
       <c r="B69" s="7" t="n"/>
+      <c r="C69" s="7" t="n"/>
+      <c r="D69" s="7" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n"/>
       <c r="B70" s="7" t="n"/>
+      <c r="C70" s="7" t="n"/>
+      <c r="D70" s="7" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="7" t="n"/>
       <c r="B71" s="7" t="n"/>
+      <c r="C71" s="7" t="n"/>
+      <c r="D71" s="7" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="7" t="n"/>
       <c r="B72" s="7" t="n"/>
+      <c r="C72" s="7" t="n"/>
+      <c r="D72" s="7" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="7" t="n"/>
       <c r="B73" s="7" t="n"/>
+      <c r="C73" s="7" t="n"/>
+      <c r="D73" s="7" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n"/>
       <c r="B74" s="7" t="n"/>
+      <c r="C74" s="7" t="n"/>
+      <c r="D74" s="7" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="7" t="n"/>
       <c r="B75" s="7" t="n"/>
+      <c r="C75" s="7" t="n"/>
+      <c r="D75" s="7" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="C11:C40" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="入力エラー" error="リストから選んでください" type="list">
-      <formula1>"在籍,体験入店"</formula1>
+    <dataValidation sqref="D11:D40" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="入力エラー" error="リストから選んでください" type="list">
+      <formula1>"在籍,体験入店,派遣,日払い"</formula1>
     </dataValidation>
-    <dataValidation sqref="B46:B75" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="入力エラー" error="リストから選んでください" type="list">
+    <dataValidation sqref="C46:C75" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="入力エラー" error="リストから選んでください" type="list">
       <formula1>"ボーイ,キッチン,店長,その他"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D42"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>キャスト別バック</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>店舗名</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>※灰色の行は記入例です。消して上書きするか、下の空欄に書いてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>※基本は、訪問時にお店の方がPOSへ入力します</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>※先に送る場合だけ、書いてください</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>※時給や本名などの個人情報は書かないでください</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>※書き終わったら、このファイル(またはシートのリンク)をLINEで送ってください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>キャストごとのバック</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>源氏名</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>バックの種類</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>単位</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>金額または率</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>ココ</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>指名</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>円</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>ココ</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>ドリンク</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="n"/>
+      <c r="B13" s="7" t="n"/>
+      <c r="C13" s="7" t="n"/>
+      <c r="D13" s="7" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="n"/>
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="7" t="n"/>
+      <c r="D14" s="7" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="n"/>
+      <c r="B15" s="7" t="n"/>
+      <c r="C15" s="7" t="n"/>
+      <c r="D15" s="7" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="n"/>
+      <c r="B16" s="7" t="n"/>
+      <c r="C16" s="7" t="n"/>
+      <c r="D16" s="7" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="n"/>
+      <c r="B17" s="7" t="n"/>
+      <c r="C17" s="7" t="n"/>
+      <c r="D17" s="7" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="n"/>
+      <c r="B18" s="7" t="n"/>
+      <c r="C18" s="7" t="n"/>
+      <c r="D18" s="7" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="n"/>
+      <c r="B19" s="7" t="n"/>
+      <c r="C19" s="7" t="n"/>
+      <c r="D19" s="7" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="n"/>
+      <c r="B20" s="7" t="n"/>
+      <c r="C20" s="7" t="n"/>
+      <c r="D20" s="7" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="n"/>
+      <c r="B21" s="7" t="n"/>
+      <c r="C21" s="7" t="n"/>
+      <c r="D21" s="7" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="n"/>
+      <c r="B22" s="7" t="n"/>
+      <c r="C22" s="7" t="n"/>
+      <c r="D22" s="7" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="n"/>
+      <c r="B23" s="7" t="n"/>
+      <c r="C23" s="7" t="n"/>
+      <c r="D23" s="7" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="n"/>
+      <c r="B24" s="7" t="n"/>
+      <c r="C24" s="7" t="n"/>
+      <c r="D24" s="7" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="n"/>
+      <c r="B25" s="7" t="n"/>
+      <c r="C25" s="7" t="n"/>
+      <c r="D25" s="7" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="n"/>
+      <c r="B26" s="7" t="n"/>
+      <c r="C26" s="7" t="n"/>
+      <c r="D26" s="7" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="n"/>
+      <c r="B27" s="7" t="n"/>
+      <c r="C27" s="7" t="n"/>
+      <c r="D27" s="7" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="n"/>
+      <c r="B28" s="7" t="n"/>
+      <c r="C28" s="7" t="n"/>
+      <c r="D28" s="7" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="n"/>
+      <c r="B29" s="7" t="n"/>
+      <c r="C29" s="7" t="n"/>
+      <c r="D29" s="7" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="n"/>
+      <c r="B30" s="7" t="n"/>
+      <c r="C30" s="7" t="n"/>
+      <c r="D30" s="7" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="n"/>
+      <c r="B31" s="7" t="n"/>
+      <c r="C31" s="7" t="n"/>
+      <c r="D31" s="7" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="n"/>
+      <c r="B32" s="7" t="n"/>
+      <c r="C32" s="7" t="n"/>
+      <c r="D32" s="7" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="n"/>
+      <c r="B33" s="7" t="n"/>
+      <c r="C33" s="7" t="n"/>
+      <c r="D33" s="7" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="n"/>
+      <c r="B34" s="7" t="n"/>
+      <c r="C34" s="7" t="n"/>
+      <c r="D34" s="7" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="n"/>
+      <c r="B35" s="7" t="n"/>
+      <c r="C35" s="7" t="n"/>
+      <c r="D35" s="7" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="n"/>
+      <c r="B36" s="7" t="n"/>
+      <c r="C36" s="7" t="n"/>
+      <c r="D36" s="7" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="n"/>
+      <c r="B37" s="7" t="n"/>
+      <c r="C37" s="7" t="n"/>
+      <c r="D37" s="7" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="n"/>
+      <c r="B38" s="7" t="n"/>
+      <c r="C38" s="7" t="n"/>
+      <c r="D38" s="7" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="n"/>
+      <c r="B39" s="7" t="n"/>
+      <c r="C39" s="7" t="n"/>
+      <c r="D39" s="7" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="n"/>
+      <c r="B40" s="7" t="n"/>
+      <c r="C40" s="7" t="n"/>
+      <c r="D40" s="7" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="n"/>
+      <c r="B41" s="7" t="n"/>
+      <c r="C41" s="7" t="n"/>
+      <c r="D41" s="7" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="n"/>
+      <c r="B42" s="7" t="n"/>
+      <c r="C42" s="7" t="n"/>
+      <c r="D42" s="7" t="n"/>
+    </row>
+  </sheetData>
+  <dataValidations count="3">
+    <dataValidation sqref="B13:B42" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="入力エラー" error="リストから選んでください" type="list">
+      <formula1>"セット,延長,指名,担当卓の売上,ドリンク,ボトル,フード"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C13:C42" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="入力エラー" error="リストから選んでください" type="list">
+      <formula1>"円,%"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D13:D42" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="入力エラー" error="0以上の数字で入力してください" type="decimal" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/templates/excel/初期設定_記入シート.xlsx
+++ b/templates/excel/初期設定_記入シート.xlsx
@@ -531,7 +531,7 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>※書き終わったら、このファイル(またはシートのリンク)をLINEで送ってください。</t>
+          <t>※書き終わったら、このファイルをLINEで送ってください。</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>※書き終わったら、このファイル(またはシートのリンク)をLINEで送ってください。</t>
+          <t>※書き終わったら、このファイルをLINEで送ってください。</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>※書き終わったら、このファイル(またはシートのリンク)をLINEで送ってください。</t>
+          <t>※書き終わったら、このファイルをLINEで送ってください。</t>
         </is>
       </c>
     </row>
